--- a/WLC_Benchmarks.xlsx
+++ b/WLC_Benchmarks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\OneDrive - KU Leuven\Dokumente\IWU\Literatur\LCA Benchmarks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Documents\GitHub\WLC-Benchmarks-for-German-Domestic-and-Non-Domestic-Buildings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C226AE0-2326-4874-B4AC-79E7368B0FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B297CA-6F1A-434F-83F8-D0A34E943010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2010" windowWidth="29040" windowHeight="15720" tabRatio="759" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,46 +43,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={89119FD1-22EC-492F-A5EF-B4B4695994C7}</author>
-    <author>tc={71F4D4A2-3F1A-4966-AD21-366F8E3A5750}</author>
-    <author>tc={D0423A2F-356C-4B30-B4F2-75E4FF340583}</author>
-    <author>tc={9F11FFF2-9807-4FB7-A899-BB33E14D8183}</author>
     <author>tc={2B1994F7-F1AC-49A1-A8FA-3E72AFA8BADC}</author>
   </authors>
   <commentList>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{89119FD1-22EC-492F-A5EF-B4B4695994C7}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="1" shapeId="0" xr:uid="{71F4D4A2-3F1A-4966-AD21-366F8E3A5750}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</t>
-      </text>
-    </comment>
-    <comment ref="F22" authorId="2" shapeId="0" xr:uid="{D0423A2F-356C-4B30-B4F2-75E4FF340583}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</t>
-      </text>
-    </comment>
-    <comment ref="I22" authorId="3" shapeId="0" xr:uid="{9F11FFF2-9807-4FB7-A899-BB33E14D8183}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</t>
-      </text>
-    </comment>
-    <comment ref="I42" authorId="4" shapeId="0" xr:uid="{2B1994F7-F1AC-49A1-A8FA-3E72AFA8BADC}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{2B1994F7-F1AC-49A1-A8FA-3E72AFA8BADC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -95,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="242">
   <si>
     <t>Wohnen</t>
   </si>
@@ -328,9 +292,6 @@
     <t>Summe</t>
   </si>
   <si>
-    <t>60 Jahre Bilanzierungszeitraum</t>
-  </si>
-  <si>
     <t>Mittelschule</t>
   </si>
   <si>
@@ -392,35 +353,6 @@
   </si>
   <si>
     <t>not enough data in Röcks original dataset (1, so use of the dataset of https://app.powerbi.com/view?r=eyJrIjoiZTFlOGFlMWMtNWI4NC00YWI2LWE5MGYtMzMzNzYzMjE2YTY4IiwidCI6ImM4ODIzYzkxLWJlODEtNGY4OS1iMDI0LTZjM2RkNzg5YzEwNiIsImMiOjh9&amp;pageName=71e5cd5bb290e8565659)</t>
-  </si>
-  <si>
-    <t>THGE [kg/mEBF²a]</t>
-  </si>
-  <si>
-    <r>
-      <t>THGE [kg/m</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BGF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>²a]</t>
-    </r>
   </si>
   <si>
     <t>alle BAK</t>
@@ -681,35 +613,6 @@
       </rPr>
       <t>·a)]</t>
     </r>
-  </si>
-  <si>
-    <t>Target values for new constructions</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>50 Jahre</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bilanzierungszeitraum</t>
-    </r>
-  </si>
-  <si>
-    <t>Target values for renovations</t>
   </si>
   <si>
     <t>THGE [kg/mBGF²a]</t>
@@ -1097,9 +1000,6 @@
     <t>Although the category "Hotel and resort" was analysed in hte study by Röck et al 2022 [4], too few datapoints are available and the average is already very close to the target value -&gt; assumption: value similar to average of "Health and Care"</t>
   </si>
   <si>
-    <t>Floor area harmonization factor</t>
-  </si>
-  <si>
     <t>Only a few data points available in the analysis by Röck et al. → Assumption: Average of the category ‘School and Daycare’ from the statistical analysis by Röck et al. 2022 [4] → Justification: typically larger rooms</t>
   </si>
   <si>
@@ -1112,9 +1012,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="0;\-0;"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0;\-0;"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="40" x14ac:knownFonts="1">
     <font>
@@ -1899,7 +1799,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1950,7 +1849,7 @@
     <xf numFmtId="0" fontId="23" fillId="13" borderId="11" xfId="6" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="12" xfId="7" applyNumberFormat="1">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="12" xfId="7" applyNumberFormat="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1962,10 +1861,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="12" xfId="7" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="12" xfId="7" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="5" applyFont="1" applyAlignment="1">
@@ -1977,19 +1876,19 @@
     <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="12" borderId="16" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="32" fillId="12" borderId="16" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="11" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="34" fillId="11" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="11" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="34" fillId="11" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="11" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="34" fillId="11" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="11" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="34" fillId="11" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="11" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2061,20 +1960,35 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="17" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="19" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="20" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="22" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="18" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -2112,26 +2026,10 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="17" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="19" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="20" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="22" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="18" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -4587,19 +4485,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F2" dT="2025-08-07T12:17:38.48" personId="{B163D503-688F-43A0-83B2-955DD70FCA75}" id="{89119FD1-22EC-492F-A5EF-B4B4695994C7}">
-    <text>Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</text>
-  </threadedComment>
-  <threadedComment ref="I2" dT="2025-08-07T12:17:38.48" personId="{B163D503-688F-43A0-83B2-955DD70FCA75}" id="{71F4D4A2-3F1A-4966-AD21-366F8E3A5750}">
-    <text>Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</text>
-  </threadedComment>
-  <threadedComment ref="F22" dT="2025-08-07T12:17:38.48" personId="{B163D503-688F-43A0-83B2-955DD70FCA75}" id="{D0423A2F-356C-4B30-B4F2-75E4FF340583}">
-    <text>Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</text>
-  </threadedComment>
-  <threadedComment ref="I22" dT="2025-08-07T12:17:38.48" personId="{B163D503-688F-43A0-83B2-955DD70FCA75}" id="{9F11FFF2-9807-4FB7-A899-BB33E14D8183}">
-    <text>Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</text>
-  </threadedComment>
-  <threadedComment ref="I42" dT="2025-08-07T12:17:38.48" personId="{B163D503-688F-43A0-83B2-955DD70FCA75}" id="{2B1994F7-F1AC-49A1-A8FA-3E72AFA8BADC}">
+  <threadedComment ref="I1" dT="2025-08-07T12:17:38.48" personId="{B163D503-688F-43A0-83B2-955DD70FCA75}" id="{2B1994F7-F1AC-49A1-A8FA-3E72AFA8BADC}">
     <text>Harmonization based on Röck et al. 2020 „Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation“</text>
   </threadedComment>
 </ThreadedComments>
@@ -4629,23 +4515,23 @@
   <sheetData>
     <row r="1" spans="1:47" s="26" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="25" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M1" s="28"/>
     </row>
     <row r="2" spans="1:47" s="26" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="M2" s="86"/>
+        <v>179</v>
+      </c>
+      <c r="M2" s="85"/>
     </row>
     <row r="3" spans="1:47" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
-      <c r="M3" s="86"/>
+      <c r="M3" s="85"/>
     </row>
     <row r="4" spans="1:47" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
-      <c r="M4" s="86"/>
+      <c r="M4" s="85"/>
     </row>
     <row r="5" spans="1:47" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28"/>
@@ -4655,71 +4541,71 @@
     </row>
     <row r="7" spans="1:47" s="26" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="27" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:47" s="26" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="B10" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="36"/>
+      <c r="B10" s="88" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="35"/>
       <c r="L10" s="6"/>
-      <c r="N10" s="94" t="s">
-        <v>162</v>
-      </c>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
-      <c r="S10" s="94"/>
-      <c r="T10" s="94"/>
-      <c r="U10" s="94"/>
-      <c r="V10" s="94"/>
-      <c r="W10" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="X10" s="88"/>
-      <c r="Y10" s="88"/>
-      <c r="Z10" s="88"/>
-      <c r="AA10" s="88"/>
-      <c r="AB10" s="88"/>
-      <c r="AC10" s="88"/>
-      <c r="AE10" s="95" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF10" s="95"/>
-      <c r="AG10" s="95"/>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="95"/>
-      <c r="AJ10" s="95"/>
-      <c r="AK10" s="95"/>
-      <c r="AL10" s="95"/>
-      <c r="AM10" s="95"/>
-      <c r="AN10" s="95"/>
-      <c r="AO10" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="AP10" s="88"/>
-      <c r="AQ10" s="88"/>
-      <c r="AR10" s="88"/>
-      <c r="AS10" s="88"/>
-      <c r="AT10" s="88"/>
-      <c r="AU10" s="88"/>
+      <c r="N10" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="O10" s="93"/>
+      <c r="P10" s="93"/>
+      <c r="Q10" s="93"/>
+      <c r="R10" s="93"/>
+      <c r="S10" s="93"/>
+      <c r="T10" s="93"/>
+      <c r="U10" s="93"/>
+      <c r="V10" s="93"/>
+      <c r="W10" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="X10" s="87"/>
+      <c r="Y10" s="87"/>
+      <c r="Z10" s="87"/>
+      <c r="AA10" s="87"/>
+      <c r="AB10" s="87"/>
+      <c r="AC10" s="87"/>
+      <c r="AE10" s="94" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF10" s="94"/>
+      <c r="AG10" s="94"/>
+      <c r="AH10" s="94"/>
+      <c r="AI10" s="94"/>
+      <c r="AJ10" s="94"/>
+      <c r="AK10" s="94"/>
+      <c r="AL10" s="94"/>
+      <c r="AM10" s="94"/>
+      <c r="AN10" s="94"/>
+      <c r="AO10" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP10" s="87"/>
+      <c r="AQ10" s="87"/>
+      <c r="AR10" s="87"/>
+      <c r="AS10" s="87"/>
+      <c r="AT10" s="87"/>
+      <c r="AU10" s="87"/>
     </row>
     <row r="11" spans="1:47" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="80" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="80"/>
+      <c r="B11" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="79"/>
       <c r="D11" s="17" t="s">
         <v>67</v>
       </c>
@@ -4741,10 +4627,10 @@
       <c r="J11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="N11" s="93" t="s">
-        <v>163</v>
-      </c>
-      <c r="O11" s="93"/>
+      <c r="N11" s="92" t="s">
+        <v>157</v>
+      </c>
+      <c r="O11" s="92"/>
       <c r="P11" s="17" t="s">
         <v>67</v>
       </c>
@@ -4787,10 +4673,10 @@
       <c r="AC11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="AE11" s="93" t="s">
-        <v>183</v>
-      </c>
-      <c r="AF11" s="93"/>
+      <c r="AE11" s="92" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF11" s="92"/>
       <c r="AG11" s="9" t="s">
         <v>40</v>
       </c>
@@ -4838,13 +4724,13 @@
       </c>
     </row>
     <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="81" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D12" s="34">
+      <c r="B12" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="117" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="118">
         <f t="shared" ref="D12:D24" si="0">IF(OR(ISBLANK(P12),ISBLANK(AH12)),"",P12+AH12)</f>
         <v>0</v>
       </c>
@@ -4872,22 +4758,22 @@
         <f t="shared" ref="J12:J24" si="4">IF(OR(ISBLANK(V12),ISBLANK(AN12)),"",V12+AN12)</f>
         <v>61.341816039184593</v>
       </c>
-      <c r="K12" s="73"/>
-      <c r="N12" s="92" t="s">
-        <v>153</v>
+      <c r="K12" s="72"/>
+      <c r="N12" s="91" t="s">
+        <v>150</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
       </c>
       <c r="Q12" s="31">
-        <f>'SIA 390'!J46</f>
+        <f>'SIA 390'!J5</f>
         <v>2.16</v>
       </c>
       <c r="R12" s="31">
-        <f>'SIA 390'!J45</f>
+        <f>'SIA 390'!J4</f>
         <v>3.24</v>
       </c>
       <c r="S12" s="13">
@@ -4907,42 +4793,42 @@
         <v>48.138302179184592</v>
       </c>
       <c r="W12" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X12" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y12" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z12" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X12" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y12" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z12" s="21" t="s">
+      <c r="AA12" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="AA12" s="22" t="s">
-        <v>173</v>
-      </c>
       <c r="AB12" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC12" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE12" s="92" t="s">
-        <v>153</v>
+        <v>169</v>
+      </c>
+      <c r="AE12" s="91" t="s">
+        <v>150</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AG12" s="19"/>
       <c r="AH12" s="7">
         <v>0</v>
       </c>
       <c r="AI12" s="13">
-        <f>'SIA 390'!I46</f>
+        <f>'SIA 390'!I5</f>
         <v>5.4</v>
       </c>
       <c r="AJ12" s="13">
-        <f>'SIA 390'!I45</f>
+        <f>'SIA 390'!I4</f>
         <v>7.5600000000000005</v>
       </c>
       <c r="AK12" s="13">
@@ -4962,33 +4848,33 @@
         <v>13.203513860000001</v>
       </c>
       <c r="AO12" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP12" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="AQ12" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="AR12" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP12" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="AQ12" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="AR12" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS12" s="32" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AT12" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU12" s="32" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="81"/>
-      <c r="C13" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="34">
+      <c r="B13" s="80"/>
+      <c r="C13" s="117" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5016,20 +4902,20 @@
         <f t="shared" si="4"/>
         <v>54.41689628962029</v>
       </c>
-      <c r="K13" s="73"/>
-      <c r="N13" s="92"/>
+      <c r="K13" s="72"/>
+      <c r="N13" s="91"/>
       <c r="O13" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P13" s="7">
         <v>0</v>
       </c>
       <c r="Q13" s="31">
-        <f>'SIA 390'!J46</f>
+        <f>'SIA 390'!J5</f>
         <v>2.16</v>
       </c>
       <c r="R13" s="31">
-        <f>'SIA 390'!J45</f>
+        <f>'SIA 390'!J4</f>
         <v>3.24</v>
       </c>
       <c r="S13" s="13">
@@ -5049,40 +4935,40 @@
         <v>34.817652369620291</v>
       </c>
       <c r="W13" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X13" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y13" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z13" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X13" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y13" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z13" s="21" t="s">
+      <c r="AA13" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="AA13" s="22" t="s">
-        <v>173</v>
-      </c>
       <c r="AB13" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC13" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE13" s="92"/>
+        <v>169</v>
+      </c>
+      <c r="AE13" s="91"/>
       <c r="AF13" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AG13" s="19"/>
       <c r="AH13" s="7">
         <v>0</v>
       </c>
       <c r="AI13" s="13">
-        <f>'SIA 390'!I46</f>
+        <f>'SIA 390'!I5</f>
         <v>5.4</v>
       </c>
       <c r="AJ13" s="13">
-        <f>'SIA 390'!I45</f>
+        <f>'SIA 390'!I4</f>
         <v>7.5600000000000005</v>
       </c>
       <c r="AK13" s="13">
@@ -5102,35 +4988,35 @@
         <v>19.599243919999999</v>
       </c>
       <c r="AO13" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP13" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="AQ13" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="AR13" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP13" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="AQ13" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="AR13" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS13" s="32" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AT13" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU13" s="32" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="81" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="34">
+      <c r="B14" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5158,21 +5044,21 @@
         <f t="shared" si="4"/>
         <v>88.365071821953407</v>
       </c>
-      <c r="N14" s="92" t="s">
-        <v>154</v>
+      <c r="N14" s="91" t="s">
+        <v>151</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P14" s="7">
         <v>0</v>
       </c>
       <c r="Q14" s="31">
-        <f>'SIA 390'!J46</f>
+        <f>'SIA 390'!J5</f>
         <v>2.16</v>
       </c>
       <c r="R14" s="31">
-        <f>'SIA 390'!J45</f>
+        <f>'SIA 390'!J4</f>
         <v>3.24</v>
       </c>
       <c r="S14" s="13">
@@ -5192,42 +5078,42 @@
         <v>70.372057291953411</v>
       </c>
       <c r="W14" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X14" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y14" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z14" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X14" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y14" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z14" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA14" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB14" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC14" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE14" s="92" t="s">
-        <v>154</v>
+        <v>166</v>
+      </c>
+      <c r="AE14" s="91" t="s">
+        <v>151</v>
       </c>
       <c r="AF14" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG14" s="19"/>
       <c r="AH14" s="7">
         <v>0</v>
       </c>
       <c r="AI14" s="13">
-        <f>'SIA 390'!I48</f>
+        <f>'SIA 390'!I7</f>
         <v>5.4</v>
       </c>
       <c r="AJ14" s="13">
-        <f>'SIA 390'!I47</f>
+        <f>'SIA 390'!I6</f>
         <v>7.5600000000000005</v>
       </c>
       <c r="AK14" s="13">
@@ -5247,33 +5133,33 @@
         <v>17.99301453</v>
       </c>
       <c r="AO14" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP14" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="AQ14" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR14" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP14" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="AQ14" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="AR14" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS14" s="32" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AT14" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU14" s="32" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="81"/>
-      <c r="C15" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" s="34">
+      <c r="B15" s="80"/>
+      <c r="C15" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5301,19 +5187,19 @@
         <f t="shared" si="4"/>
         <v>111.425732936144</v>
       </c>
-      <c r="N15" s="92"/>
+      <c r="N15" s="91"/>
       <c r="O15" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P15" s="7">
         <v>0</v>
       </c>
       <c r="Q15" s="31">
-        <f>AVERAGE('SIA 390'!J48,'SIA 390'!J50,'SIA 390'!J52,'SIA 390'!J54)</f>
+        <f>AVERAGE('SIA 390'!J7,'SIA 390'!J9,'SIA 390'!J11,'SIA 390'!J13)</f>
         <v>2.7</v>
       </c>
       <c r="R15" s="31">
-        <f>AVERAGE('SIA 390'!J47,'SIA 390'!J49,'SIA 390'!J51,'SIA 390'!J53)</f>
+        <f>AVERAGE('SIA 390'!J6,'SIA 390'!J8,'SIA 390'!J10,'SIA 390'!J12)</f>
         <v>3.7800000000000002</v>
       </c>
       <c r="S15" s="13">
@@ -5333,29 +5219,29 @@
         <v>89.015145871144</v>
       </c>
       <c r="W15" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X15" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y15" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z15" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X15" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y15" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z15" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA15" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB15" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC15" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE15" s="92"/>
+        <v>166</v>
+      </c>
+      <c r="AE15" s="91"/>
       <c r="AF15" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AG15" s="19"/>
       <c r="AH15" s="7">
@@ -5386,33 +5272,33 @@
         <v>22.410587065000001</v>
       </c>
       <c r="AO15" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP15" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ15" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR15" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP15" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AQ15" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR15" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS15" s="29" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AT15" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU15" s="29" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="81"/>
-      <c r="C16" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="34">
+      <c r="B16" s="80"/>
+      <c r="C16" s="117" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5440,19 +5326,19 @@
         <f t="shared" si="4"/>
         <v>111.81380669888595</v>
       </c>
-      <c r="N16" s="92"/>
+      <c r="N16" s="91"/>
       <c r="O16" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="P16" s="7">
         <v>0</v>
       </c>
       <c r="Q16" s="31">
-        <f>'SIA 390'!J60</f>
+        <f>'SIA 390'!J19</f>
         <v>6.48</v>
       </c>
       <c r="R16" s="31">
-        <f>'SIA 390'!J59</f>
+        <f>'SIA 390'!J18</f>
         <v>8.64</v>
       </c>
       <c r="S16" s="13">
@@ -5472,32 +5358,32 @@
         <v>90.613079268885954</v>
       </c>
       <c r="W16" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X16" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y16" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z16" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X16" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y16" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z16" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA16" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB16" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC16" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE16" s="92"/>
+        <v>166</v>
+      </c>
+      <c r="AE16" s="91"/>
       <c r="AF16" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AG16" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AH16" s="7">
         <v>0</v>
@@ -5527,33 +5413,33 @@
         <v>21.200727430000001</v>
       </c>
       <c r="AO16" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP16" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ16" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR16" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP16" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AQ16" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR16" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS16" s="32" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AT16" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU16" s="32" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="81"/>
-      <c r="C17" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="34">
+      <c r="B17" s="80"/>
+      <c r="C17" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5581,19 +5467,19 @@
         <f t="shared" si="4"/>
         <v>95.246430405212237</v>
       </c>
-      <c r="N17" s="92"/>
+      <c r="N17" s="91"/>
       <c r="O17" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P17" s="7">
         <v>0</v>
       </c>
       <c r="Q17" s="31">
-        <f>AVERAGE('SIA 390'!J50,'SIA 390'!J52,'SIA 390'!J54)</f>
+        <f>AVERAGE('SIA 390'!J9,'SIA 390'!J11,'SIA 390'!J13)</f>
         <v>2.52</v>
       </c>
       <c r="R17" s="31">
-        <f>AVERAGE('SIA 390'!J49,'SIA 390'!J51,'SIA 390'!J53)</f>
+        <f>AVERAGE('SIA 390'!J8,'SIA 390'!J10,'SIA 390'!J12)</f>
         <v>3.6</v>
       </c>
       <c r="S17" s="13">
@@ -5613,40 +5499,40 @@
         <v>68.418270805212245</v>
       </c>
       <c r="W17" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X17" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y17" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z17" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X17" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y17" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z17" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA17" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB17" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC17" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE17" s="92"/>
+        <v>166</v>
+      </c>
+      <c r="AE17" s="91"/>
       <c r="AF17" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AG17" s="19"/>
       <c r="AH17" s="7">
         <v>0</v>
       </c>
       <c r="AI17" s="13">
-        <f>AVERAGE('SIA 390'!I50,'SIA 390'!I52,'SIA 390'!I54)</f>
+        <f>AVERAGE('SIA 390'!I9,'SIA 390'!I11,'SIA 390'!I13)</f>
         <v>5.4000000000000012</v>
       </c>
       <c r="AJ17" s="13">
-        <f>AVERAGE('SIA 390'!I49,'SIA 390'!I51,'SIA 390'!I53)</f>
+        <f>AVERAGE('SIA 390'!I8,'SIA 390'!I10,'SIA 390'!I12)</f>
         <v>7.56</v>
       </c>
       <c r="AK17" s="13">
@@ -5666,33 +5552,33 @@
         <v>26.828159599999999</v>
       </c>
       <c r="AO17" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP17" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ17" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="AR17" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP17" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="AQ17" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="AR17" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS17" s="32" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AT17" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU17" s="32" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="81"/>
-      <c r="C18" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="34">
+      <c r="B18" s="80"/>
+      <c r="C18" s="117" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5720,9 +5606,9 @@
         <f t="shared" si="4"/>
         <v>149.9465587454348</v>
       </c>
-      <c r="N18" s="92"/>
+      <c r="N18" s="91"/>
       <c r="O18" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P18" s="7">
         <v>0</v>
@@ -5752,32 +5638,32 @@
         <v>123.11839914543479</v>
       </c>
       <c r="W18" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X18" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y18" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z18" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X18" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y18" s="23" t="s">
+      <c r="AA18" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="Z18" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA18" s="22" t="s">
-        <v>172</v>
-      </c>
       <c r="AB18" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC18" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE18" s="92"/>
+        <v>166</v>
+      </c>
+      <c r="AE18" s="91"/>
       <c r="AF18" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AG18" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AH18" s="7">
         <v>0</v>
@@ -5807,33 +5693,33 @@
         <v>26.828159599999999</v>
       </c>
       <c r="AO18" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP18" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ18" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR18" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP18" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AQ18" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR18" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS18" s="29" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AT18" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU18" s="29" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="81"/>
-      <c r="C19" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="34">
+      <c r="B19" s="80"/>
+      <c r="C19" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5861,9 +5747,9 @@
         <f t="shared" si="4"/>
         <v>84.000885302957471</v>
       </c>
-      <c r="N19" s="92"/>
+      <c r="N19" s="91"/>
       <c r="O19" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P19" s="7">
         <v>0</v>
@@ -5893,33 +5779,33 @@
         <v>63.826179422957473</v>
       </c>
       <c r="W19" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X19" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y19" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z19" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X19" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y19" s="23" t="s">
+      <c r="AA19" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="Z19" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA19" s="22" t="s">
-        <v>172</v>
-      </c>
       <c r="AB19" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC19" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD19" s="16"/>
-      <c r="AE19" s="92"/>
+      <c r="AE19" s="91"/>
       <c r="AF19" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AG19" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AH19" s="7">
         <v>0</v>
@@ -5949,33 +5835,33 @@
         <v>20.174705879999998</v>
       </c>
       <c r="AO19" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP19" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ19" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR19" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP19" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AQ19" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR19" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS19" s="32" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AT19" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU19" s="32" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="81"/>
-      <c r="C20" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="34">
+      <c r="B20" s="80"/>
+      <c r="C20" s="119" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6003,19 +5889,19 @@
         <f t="shared" si="4"/>
         <v>143.55209192155712</v>
       </c>
-      <c r="N20" s="92"/>
+      <c r="N20" s="91"/>
       <c r="O20" s="14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P20" s="7">
         <v>0</v>
       </c>
       <c r="Q20" s="31">
-        <f>'SIA 390'!J60</f>
+        <f>'SIA 390'!J19</f>
         <v>6.48</v>
       </c>
       <c r="R20" s="31">
-        <f>'SIA 390'!J59</f>
+        <f>'SIA 390'!J18</f>
         <v>8.64</v>
       </c>
       <c r="S20" s="13">
@@ -6035,43 +5921,43 @@
         <v>122.35136449155711</v>
       </c>
       <c r="W20" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X20" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y20" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z20" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X20" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y20" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z20" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA20" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB20" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC20" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD20" s="16"/>
-      <c r="AE20" s="92"/>
+      <c r="AE20" s="91"/>
       <c r="AF20" s="14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AG20" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AH20" s="7">
         <v>0</v>
       </c>
       <c r="AI20" s="13">
-        <f>'SIA 390'!I60</f>
+        <f>'SIA 390'!I19</f>
         <v>5.4</v>
       </c>
       <c r="AJ20" s="13">
-        <f>'SIA 390'!I59</f>
+        <f>'SIA 390'!I18</f>
         <v>7.5600000000000005</v>
       </c>
       <c r="AK20" s="13">
@@ -6091,33 +5977,33 @@
         <v>21.200727430000001</v>
       </c>
       <c r="AO20" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP20" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="AQ20" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="AR20" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP20" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="AQ20" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="AR20" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS20" s="29" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AT20" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU20" s="29" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="81"/>
-      <c r="C21" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="34">
+      <c r="B21" s="80"/>
+      <c r="C21" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6145,19 +6031,19 @@
         <f t="shared" si="4"/>
         <v>88.438173027999127</v>
       </c>
-      <c r="N21" s="92"/>
+      <c r="N21" s="91"/>
       <c r="O21" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P21" s="7">
         <v>0</v>
       </c>
       <c r="Q21" s="31">
-        <f>'SIA 390'!J56</f>
+        <f>'SIA 390'!J15</f>
         <v>3.24</v>
       </c>
       <c r="R21" s="31">
-        <f>'SIA 390'!J55</f>
+        <f>'SIA 390'!J14</f>
         <v>6.48</v>
       </c>
       <c r="S21" s="13">
@@ -6177,41 +6063,41 @@
         <v>74.634644027999144</v>
       </c>
       <c r="W21" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X21" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y21" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z21" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X21" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y21" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z21" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA21" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB21" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC21" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD21" s="16"/>
-      <c r="AE21" s="92"/>
+      <c r="AE21" s="91"/>
       <c r="AF21" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AG21" s="19"/>
       <c r="AH21" s="7">
         <v>0</v>
       </c>
       <c r="AI21" s="13">
-        <f>'SIA 390'!I56</f>
+        <f>'SIA 390'!I15</f>
         <v>5.4</v>
       </c>
       <c r="AJ21" s="13">
-        <f>'SIA 390'!I55</f>
+        <f>'SIA 390'!I14</f>
         <v>7.5600000000000005</v>
       </c>
       <c r="AK21" s="13">
@@ -6231,33 +6117,33 @@
         <v>13.80352899999998</v>
       </c>
       <c r="AO21" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP21" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="AQ21" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR21" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP21" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="AQ21" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="AR21" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS21" s="32" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AT21" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU21" s="32" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="81"/>
-      <c r="C22" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="34">
+      <c r="B22" s="80"/>
+      <c r="C22" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6288,9 +6174,9 @@
       <c r="K22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="N22" s="92"/>
+      <c r="N22" s="91"/>
       <c r="O22" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P22" s="7">
         <v>0</v>
@@ -6320,30 +6206,30 @@
         <v>115.43861742226559</v>
       </c>
       <c r="W22" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X22" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y22" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z22" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X22" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y22" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Z22" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA22" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB22" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC22" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD22" s="16"/>
-      <c r="AE22" s="92"/>
+      <c r="AE22" s="91"/>
       <c r="AF22" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG22" s="19"/>
       <c r="AH22" s="7">
@@ -6375,33 +6261,33 @@
         <v>13.80352899999998</v>
       </c>
       <c r="AO22" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP22" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ22" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR22" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP22" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AQ22" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR22" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS22" s="29" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AT22" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU22" s="29" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="81"/>
-      <c r="C23" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D23" s="34">
+      <c r="B23" s="80"/>
+      <c r="C23" s="117" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6430,9 +6316,9 @@
         <v>121.90175607977368</v>
       </c>
       <c r="K23" s="10"/>
-      <c r="N23" s="92"/>
+      <c r="N23" s="91"/>
       <c r="O23" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P23" s="7">
         <v>0</v>
@@ -6462,30 +6348,30 @@
         <v>108.09822707977369</v>
       </c>
       <c r="W23" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X23" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y23" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z23" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X23" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y23" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Z23" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA23" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB23" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC23" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD23" s="16"/>
-      <c r="AE23" s="92"/>
+      <c r="AE23" s="91"/>
       <c r="AF23" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AG23" s="19"/>
       <c r="AH23" s="7">
@@ -6517,33 +6403,33 @@
         <v>13.80352899999998</v>
       </c>
       <c r="AO23" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP23" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ23" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR23" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP23" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AQ23" s="30" t="s">
+      <c r="AS23" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="AT23" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AU23" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="AR23" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="AS23" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="AT23" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="AU23" s="29" t="s">
-        <v>223</v>
-      </c>
     </row>
     <row r="24" spans="2:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="81"/>
-      <c r="C24" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="34">
+      <c r="B24" s="80"/>
+      <c r="C24" s="117" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6572,9 +6458,9 @@
         <v>135.27389110989566</v>
       </c>
       <c r="K24" s="10"/>
-      <c r="N24" s="92"/>
+      <c r="N24" s="91"/>
       <c r="O24" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P24" s="7">
         <v>0</v>
@@ -6604,30 +6490,30 @@
         <v>107.66683310989571</v>
       </c>
       <c r="W24" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="X24" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y24" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z24" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="X24" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y24" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Z24" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AA24" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AB24" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC24" s="22" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD24" s="16"/>
-      <c r="AE24" s="92"/>
+      <c r="AE24" s="91"/>
       <c r="AF24" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AG24" s="19"/>
       <c r="AH24" s="7">
@@ -6659,25 +6545,25 @@
         <v>27.607057999999959</v>
       </c>
       <c r="AO24" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP24" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ24" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR24" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AP24" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AQ24" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR24" s="21" t="s">
-        <v>167</v>
-      </c>
       <c r="AS24" s="29" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AT24" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AU24" s="29" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="2:47" x14ac:dyDescent="0.3">
@@ -6688,523 +6574,523 @@
       <c r="AE25" s="20"/>
     </row>
     <row r="26" spans="2:47" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="X26" s="83" t="s">
-        <v>179</v>
+      <c r="X26" s="82" t="s">
+        <v>173</v>
       </c>
       <c r="Y26" s="20"/>
-      <c r="Z26" s="84" t="s">
-        <v>180</v>
+      <c r="Z26" s="83" t="s">
+        <v>174</v>
       </c>
       <c r="AA26" s="20"/>
       <c r="AG26" s="16"/>
-      <c r="AO26" s="87"/>
+      <c r="AO26" s="86"/>
     </row>
     <row r="27" spans="2:47" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="X27" s="42" t="s">
-        <v>176</v>
+      <c r="X27" s="41" t="s">
+        <v>170</v>
       </c>
       <c r="Z27" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA27" s="82" t="s">
-        <v>169</v>
+        <v>162</v>
+      </c>
+      <c r="AA27" s="81" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="2:47" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="X28" s="43" t="s">
-        <v>177</v>
+      <c r="X28" s="42" t="s">
+        <v>171</v>
       </c>
       <c r="Z28" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA28" s="82" t="s">
-        <v>171</v>
+        <v>164</v>
+      </c>
+      <c r="AA28" s="81" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="2:47" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="X29" s="44" t="s">
-        <v>178</v>
+      <c r="X29" s="43" t="s">
+        <v>172</v>
       </c>
       <c r="Z29" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA29" s="85" t="s">
-        <v>190</v>
+        <v>183</v>
+      </c>
+      <c r="AA29" s="84" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="2:47" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="Z30" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA30" s="85" t="s">
-        <v>192</v>
+        <v>185</v>
+      </c>
+      <c r="AA30" s="84" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="2:47" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:47" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
     </row>
     <row r="33" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
+      <c r="B33" s="39"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="40"/>
     </row>
     <row r="34" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="40"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
+      <c r="B34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
     </row>
     <row r="35" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="40"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
+      <c r="B35" s="39"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
     </row>
     <row r="36" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="40"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
+      <c r="B36" s="39"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
     </row>
     <row r="37" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="40"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
+      <c r="B37" s="39"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
     </row>
     <row r="38" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
+      <c r="B38" s="39"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="40"/>
     </row>
     <row r="39" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="40"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
+      <c r="B39" s="39"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
     </row>
     <row r="40" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="40"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="41"/>
+      <c r="B40" s="39"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
     </row>
     <row r="41" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="40"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
+      <c r="B41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
     </row>
     <row r="42" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="40"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
+      <c r="B42" s="39"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="40"/>
     </row>
     <row r="43" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="40"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
+      <c r="B43" s="39"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="40"/>
     </row>
     <row r="44" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="40"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
+      <c r="B44" s="39"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="40"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="40"/>
     </row>
     <row r="45" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="40"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
+      <c r="B45" s="39"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
     </row>
     <row r="46" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
     </row>
     <row r="48" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="40"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="41"/>
+      <c r="B48" s="39"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="40"/>
     </row>
     <row r="49" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="40"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
+      <c r="B49" s="39"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="40"/>
     </row>
     <row r="50" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="40"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
+      <c r="B50" s="39"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
     </row>
     <row r="51" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="40"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
+      <c r="B51" s="39"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
     </row>
     <row r="52" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="40"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
+      <c r="B52" s="39"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="40"/>
     </row>
     <row r="53" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="40"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
+      <c r="B53" s="39"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="40"/>
     </row>
     <row r="54" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="40"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
+      <c r="B54" s="39"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40"/>
     </row>
     <row r="55" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="40"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
+      <c r="B55" s="39"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40"/>
     </row>
     <row r="56" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="40"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
-      <c r="L56" s="41"/>
+      <c r="B56" s="39"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="40"/>
     </row>
     <row r="57" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="40"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="41"/>
+      <c r="B57" s="39"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="40"/>
     </row>
     <row r="58" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="40"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
-      <c r="L58" s="41"/>
+      <c r="B58" s="39"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="40"/>
     </row>
     <row r="59" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="40"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="41"/>
-      <c r="J59" s="41"/>
-      <c r="K59" s="41"/>
-      <c r="L59" s="41"/>
+      <c r="B59" s="39"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="40"/>
     </row>
     <row r="60" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="40"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="41"/>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
-      <c r="L60" s="41"/>
+      <c r="B60" s="39"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="40"/>
     </row>
     <row r="61" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="41"/>
-      <c r="J61" s="41"/>
-      <c r="K61" s="41"/>
-      <c r="L61" s="41"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="40"/>
     </row>
     <row r="62" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="63" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="45"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
+      <c r="J63" s="44"/>
     </row>
     <row r="64" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="40"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="41"/>
-      <c r="I64" s="41"/>
-      <c r="J64" s="41"/>
-      <c r="K64" s="41"/>
-      <c r="L64" s="41"/>
+      <c r="B64" s="39"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="40"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="40"/>
+      <c r="L64" s="40"/>
     </row>
     <row r="65" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="40"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="41"/>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
-      <c r="L65" s="41"/>
+      <c r="B65" s="39"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="40"/>
+      <c r="I65" s="40"/>
+      <c r="J65" s="40"/>
+      <c r="K65" s="40"/>
+      <c r="L65" s="40"/>
     </row>
     <row r="66" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="40"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
-      <c r="L66" s="41"/>
+      <c r="B66" s="39"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
     </row>
     <row r="67" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="40"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="41"/>
-      <c r="I67" s="41"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="41"/>
-      <c r="L67" s="41"/>
+      <c r="B67" s="39"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="40"/>
+      <c r="J67" s="40"/>
+      <c r="K67" s="40"/>
+      <c r="L67" s="40"/>
     </row>
     <row r="68" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="40"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="41"/>
-      <c r="I68" s="41"/>
-      <c r="J68" s="41"/>
-      <c r="K68" s="41"/>
-      <c r="L68" s="41"/>
+      <c r="B68" s="39"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="40"/>
+      <c r="I68" s="40"/>
+      <c r="J68" s="40"/>
+      <c r="K68" s="40"/>
+      <c r="L68" s="40"/>
     </row>
     <row r="69" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="40"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="41"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
-      <c r="L69" s="41"/>
+      <c r="B69" s="39"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="40"/>
+      <c r="K69" s="40"/>
+      <c r="L69" s="40"/>
     </row>
     <row r="70" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="40"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="41"/>
-      <c r="I70" s="41"/>
-      <c r="J70" s="41"/>
-      <c r="K70" s="41"/>
-      <c r="L70" s="41"/>
+      <c r="B70" s="39"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="40"/>
+      <c r="L70" s="40"/>
     </row>
     <row r="71" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="40"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="41"/>
-      <c r="H71" s="41"/>
-      <c r="I71" s="41"/>
-      <c r="J71" s="41"/>
-      <c r="K71" s="41"/>
-      <c r="L71" s="41"/>
+      <c r="B71" s="39"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+      <c r="J71" s="40"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="40"/>
     </row>
     <row r="72" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="40"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="41"/>
-      <c r="K72" s="41"/>
-      <c r="L72" s="41"/>
+      <c r="B72" s="39"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40"/>
+      <c r="I72" s="40"/>
+      <c r="J72" s="40"/>
+      <c r="K72" s="40"/>
+      <c r="L72" s="40"/>
     </row>
     <row r="73" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="40"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
-      <c r="L73" s="41"/>
+      <c r="B73" s="39"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
+      <c r="L73" s="40"/>
     </row>
     <row r="74" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="40"/>
-      <c r="E74" s="41"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="41"/>
-      <c r="H74" s="41"/>
-      <c r="I74" s="41"/>
-      <c r="J74" s="41"/>
-      <c r="K74" s="41"/>
-      <c r="L74" s="41"/>
+      <c r="B74" s="39"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="40"/>
+      <c r="I74" s="40"/>
+      <c r="J74" s="40"/>
+      <c r="K74" s="40"/>
+      <c r="L74" s="40"/>
     </row>
     <row r="75" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="40"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="41"/>
-      <c r="H75" s="41"/>
-      <c r="I75" s="41"/>
-      <c r="J75" s="41"/>
-      <c r="K75" s="41"/>
-      <c r="L75" s="41"/>
+      <c r="B75" s="39"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
+      <c r="J75" s="40"/>
+      <c r="K75" s="40"/>
+      <c r="L75" s="40"/>
     </row>
     <row r="76" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="40"/>
-      <c r="E76" s="41"/>
-      <c r="F76" s="41"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="41"/>
-      <c r="I76" s="41"/>
-      <c r="J76" s="41"/>
-      <c r="K76" s="41"/>
-      <c r="L76" s="41"/>
+      <c r="B76" s="39"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="40"/>
+      <c r="L76" s="40"/>
     </row>
     <row r="77" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="78" spans="2:12" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -7564,9 +7450,9 @@
       <c r="M104" s="24"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C105" s="92"/>
-      <c r="D105" s="92"/>
-      <c r="E105" s="93"/>
+      <c r="C105" s="91"/>
+      <c r="D105" s="91"/>
+      <c r="E105" s="92"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E107" s="4"/>
@@ -7654,18 +7540,6 @@
     <mergeCell ref="AE14:AE24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E12:J24">
-    <cfRule type="colorScale" priority="136">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K22:L24">
     <cfRule type="colorScale" priority="135">
       <colorScale>
@@ -7689,7 +7563,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8305C46-A22D-47AF-BBBE-B8EDAFA7B6C1}">
-  <dimension ref="A2:N60"/>
+  <dimension ref="G1:K19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -7700,1846 +7574,308 @@
     <col min="9" max="11" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="100" t="s">
-        <v>156</v>
-      </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="88" t="s">
+    <row r="1" spans="7:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="95" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1" s="95"/>
+      <c r="I1" s="96" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+    </row>
+    <row r="2" spans="7:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+    </row>
+    <row r="3" spans="7:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G4" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="J4" s="47">
+        <v>3.24</v>
+      </c>
+      <c r="K4" s="47">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="5" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G5" s="97"/>
+      <c r="H5" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J5" s="47">
+        <v>2.16</v>
+      </c>
+      <c r="K5" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G6" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="J6" s="47">
+        <v>4.32</v>
+      </c>
+      <c r="K6" s="47">
+        <v>11.88</v>
+      </c>
+    </row>
+    <row r="7" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G7" s="97"/>
+      <c r="H7" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J7" s="47">
+        <v>3.24</v>
+      </c>
+      <c r="K7" s="47">
+        <v>8.64</v>
+      </c>
+    </row>
+    <row r="8" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G8" s="97" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="J8" s="47">
+        <v>3.24</v>
+      </c>
+      <c r="K8" s="47">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="9" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G9" s="97"/>
+      <c r="H9" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J9" s="47">
+        <v>2.16</v>
+      </c>
+      <c r="K9" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G10" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88" t="s">
-        <v>157</v>
-      </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88" t="s">
-        <v>84</v>
-      </c>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="N2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="100"/>
-      <c r="B3" s="100"/>
-      <c r="C3" s="88" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88" t="s">
-        <v>100</v>
-      </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="N3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="100"/>
-      <c r="B4" s="100"/>
-      <c r="C4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="H10" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="3">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3">
-        <f>C5+D5</f>
-        <v>11</v>
-      </c>
-      <c r="F5" s="3">
-        <f t="shared" ref="F5:F20" si="0">C5*60/50</f>
+      <c r="I10" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="J10" s="47">
+        <v>3.24</v>
+      </c>
+      <c r="K10" s="47">
         <v>10.8</v>
       </c>
-      <c r="G5" s="3">
-        <f t="shared" ref="G5:G20" si="1">D5*60/50</f>
-        <v>2.4</v>
-      </c>
-      <c r="H5" s="3">
-        <f>F5+G5</f>
-        <v>13.200000000000001</v>
-      </c>
-      <c r="I5" s="3">
-        <f>F5*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J5" s="3">
-        <f>G5*$N$3</f>
+    </row>
+    <row r="11" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G11" s="97"/>
+      <c r="H11" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J11" s="47">
         <v>2.16</v>
       </c>
-      <c r="K5" s="3">
-        <f>H5*$N$3</f>
+      <c r="K11" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G12" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="J12" s="47">
+        <v>4.32</v>
+      </c>
+      <c r="K12" s="47">
         <v>11.88</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="97"/>
-      <c r="B6" s="3" t="s">
+    <row r="13" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G13" s="97"/>
+      <c r="H13" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="3">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <f>C6+D6</f>
-        <v>7</v>
-      </c>
-      <c r="F6" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
-      </c>
-      <c r="H6" s="3">
-        <f>F6+G6</f>
-        <v>8.4</v>
-      </c>
-      <c r="I6" s="3">
-        <f>F6*$N$3</f>
+      <c r="I13" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J13" s="47">
+        <v>3.24</v>
+      </c>
+      <c r="K13" s="47">
+        <v>8.64</v>
+      </c>
+    </row>
+    <row r="14" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G14" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="J14" s="47">
         <v>6.48</v>
       </c>
-      <c r="J6" s="3">
-        <f>G6*$N$3</f>
-        <v>1.08</v>
-      </c>
-      <c r="K6" s="3">
-        <f>H6*$N$3</f>
+      <c r="K14" s="47">
+        <v>14.040000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G15" s="97"/>
+      <c r="H15" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J15" s="47">
+        <v>3.24</v>
+      </c>
+      <c r="K15" s="47">
+        <v>8.64</v>
+      </c>
+    </row>
+    <row r="16" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G16" s="97" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="47">
         <v>7.5600000000000005</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="97" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="J16" s="47">
+        <v>30.24</v>
+      </c>
+      <c r="K16" s="47">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G17" s="97"/>
+      <c r="H17" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J17" s="47">
+        <v>18.36</v>
+      </c>
+      <c r="K17" s="47">
+        <v>23.759999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G18" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3">
-        <f t="shared" ref="E7:E18" si="2">C7+D7</f>
-        <v>12</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>3.6</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" ref="H7:H20" si="3">F7+G7</f>
-        <v>14.4</v>
-      </c>
-      <c r="I7" s="3">
-        <f>F7*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J7" s="3">
-        <f>G7*$N$3</f>
-        <v>3.24</v>
-      </c>
-      <c r="K7" s="3">
-        <f>H7*$N$3</f>
-        <v>12.96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="97"/>
-      <c r="B8" s="3" t="s">
+      <c r="I18" s="47">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="J18" s="47">
+        <v>8.64</v>
+      </c>
+      <c r="K18" s="47">
+        <v>16.200000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G19" s="97"/>
+      <c r="H19" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="3">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="3"/>
-        <v>9.6</v>
-      </c>
-      <c r="I8" s="3">
-        <f>F8*$N$3</f>
+      <c r="I19" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="J19" s="47">
         <v>6.48</v>
       </c>
-      <c r="J8" s="3">
-        <f>G8*$N$3</f>
-        <v>2.16</v>
-      </c>
-      <c r="K8" s="3">
-        <f>H8*$N$3</f>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="97" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3">
-        <v>9</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2</v>
-      </c>
-      <c r="E9" s="3">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" si="3"/>
-        <v>13.200000000000001</v>
-      </c>
-      <c r="I9" s="3">
-        <f>F9*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J9" s="3">
-        <f>G9*$N$3</f>
-        <v>2.16</v>
-      </c>
-      <c r="K9" s="3">
-        <f>H9*$N$3</f>
-        <v>11.88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="97"/>
-      <c r="B10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="3">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="F10" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="3"/>
-        <v>8.4</v>
-      </c>
-      <c r="I10" s="3">
-        <f>F10*$N$3</f>
-        <v>6.48</v>
-      </c>
-      <c r="J10" s="3">
-        <f>G10*$N$3</f>
-        <v>1.08</v>
-      </c>
-      <c r="K10" s="3">
-        <f>H10*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="97" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="3">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2</v>
-      </c>
-      <c r="E11" s="3">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="3"/>
-        <v>13.200000000000001</v>
-      </c>
-      <c r="I11" s="3">
-        <f>F11*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J11" s="3">
-        <f>G11*$N$3</f>
-        <v>2.16</v>
-      </c>
-      <c r="K11" s="3">
-        <f>H11*$N$3</f>
-        <v>11.88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="97"/>
-      <c r="B12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="3">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="F12" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G12" s="3">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" si="3"/>
-        <v>8.4</v>
-      </c>
-      <c r="I12" s="3">
-        <f>F12*$N$3</f>
-        <v>6.48</v>
-      </c>
-      <c r="J12" s="3">
-        <f>G12*$N$3</f>
-        <v>1.08</v>
-      </c>
-      <c r="K12" s="3">
-        <f>H12*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="97" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="3">
-        <v>9</v>
-      </c>
-      <c r="D13" s="3">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="F13" s="3">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="G13" s="3">
-        <f t="shared" si="1"/>
-        <v>3.6</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="3"/>
-        <v>14.4</v>
-      </c>
-      <c r="I13" s="3">
-        <f>F13*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J13" s="3">
-        <f>G13*$N$3</f>
-        <v>3.24</v>
-      </c>
-      <c r="K13" s="3">
-        <f>H13*$N$3</f>
-        <v>12.96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="97"/>
-      <c r="B14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="3">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2</v>
-      </c>
-      <c r="E14" s="3">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G14" s="3">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="H14" s="3">
-        <f t="shared" si="3"/>
-        <v>9.6</v>
-      </c>
-      <c r="I14" s="3">
-        <f>F14*$N$3</f>
-        <v>6.48</v>
-      </c>
-      <c r="J14" s="3">
-        <f>G14*$N$3</f>
-        <v>2.16</v>
-      </c>
-      <c r="K14" s="3">
-        <f>H14*$N$3</f>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="97" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="3">
-        <v>9</v>
-      </c>
-      <c r="D15" s="3">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="F15" s="3">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="G15" s="3">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="H15" s="3">
-        <f t="shared" si="3"/>
-        <v>16.8</v>
-      </c>
-      <c r="I15" s="3">
-        <f>F15*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J15" s="3">
-        <f>G15*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="K15" s="3">
-        <f>H15*$N$3</f>
-        <v>15.120000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="97"/>
-      <c r="B16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="3">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-      <c r="E16" s="3">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="F16" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G16" s="3">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="H16" s="3">
-        <f t="shared" si="3"/>
-        <v>9.6</v>
-      </c>
-      <c r="I16" s="3">
-        <f>F16*$N$3</f>
-        <v>6.48</v>
-      </c>
-      <c r="J16" s="3">
-        <f>G16*$N$3</f>
-        <v>2.16</v>
-      </c>
-      <c r="K16" s="3">
-        <f>H16*$N$3</f>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="97" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="3">
-        <v>9</v>
-      </c>
-      <c r="D17" s="3">
-        <v>27</v>
-      </c>
-      <c r="E17" s="3">
-        <f t="shared" si="2"/>
-        <v>36</v>
-      </c>
-      <c r="F17" s="3">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="G17" s="3">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="H17" s="3">
-        <f t="shared" si="3"/>
-        <v>43.2</v>
-      </c>
-      <c r="I17" s="3">
-        <f>F17*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J17" s="3">
-        <f>G17*$N$3</f>
-        <v>29.16</v>
-      </c>
-      <c r="K17" s="3">
-        <f>H17*$N$3</f>
-        <v>38.880000000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="97"/>
-      <c r="B18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="3">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="F18" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G18" s="3">
-        <f t="shared" si="1"/>
-        <v>19.2</v>
-      </c>
-      <c r="H18" s="3">
-        <f t="shared" si="3"/>
-        <v>26.4</v>
-      </c>
-      <c r="I18" s="3">
-        <f>F18*$N$3</f>
-        <v>6.48</v>
-      </c>
-      <c r="J18" s="3">
-        <f>G18*$N$3</f>
-        <v>17.28</v>
-      </c>
-      <c r="K18" s="3">
-        <f>H18*$N$3</f>
-        <v>23.759999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="97" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="3">
-        <v>9</v>
-      </c>
-      <c r="D19" s="3">
-        <v>7</v>
-      </c>
-      <c r="E19" s="3">
-        <f>C19+D19</f>
-        <v>16</v>
-      </c>
-      <c r="F19" s="3">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="G19" s="3">
-        <f t="shared" si="1"/>
-        <v>8.4</v>
-      </c>
-      <c r="H19" s="3">
-        <f t="shared" si="3"/>
-        <v>19.200000000000003</v>
-      </c>
-      <c r="I19" s="3">
-        <f>F19*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J19" s="3">
-        <f>G19*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="K19" s="3">
-        <f>H19*$N$3</f>
-        <v>17.280000000000005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="97"/>
-      <c r="B20" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="3">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <f>C20+D20</f>
-        <v>11</v>
-      </c>
-      <c r="F20" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="G20" s="3">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="H20" s="3">
-        <f t="shared" si="3"/>
-        <v>13.2</v>
-      </c>
-      <c r="I20" s="3">
-        <f>F20*$N$3</f>
-        <v>6.48</v>
-      </c>
-      <c r="J20" s="3">
-        <f>G20*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="K20" s="3">
-        <f>H20*$N$3</f>
+      <c r="K19" s="47">
         <v>11.879999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="100" t="s">
-        <v>158</v>
-      </c>
-      <c r="B22" s="100"/>
-      <c r="C22" s="88" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="88" t="s">
-        <v>157</v>
-      </c>
-      <c r="G22" s="88"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="88" t="s">
-        <v>84</v>
-      </c>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="100"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="88" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88" t="s">
-        <v>100</v>
-      </c>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="100"/>
-      <c r="B24" s="100"/>
-      <c r="C24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="3">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3">
-        <v>4</v>
-      </c>
-      <c r="E25" s="3">
-        <f>C25+D25</f>
-        <v>9</v>
-      </c>
-      <c r="F25" s="3">
-        <f t="shared" ref="F25:F40" si="4">C25*60/50</f>
-        <v>6</v>
-      </c>
-      <c r="G25" s="3">
-        <f t="shared" ref="G25:G40" si="5">D25*60/50</f>
-        <v>4.8</v>
-      </c>
-      <c r="H25" s="3">
-        <f>F25+G25</f>
-        <v>10.8</v>
-      </c>
-      <c r="I25" s="3">
-        <f>F25*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J25" s="3">
-        <f>G25*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="K25" s="3">
-        <f>H25*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="97"/>
-      <c r="B26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="3">
-        <v>4</v>
-      </c>
-      <c r="D26" s="3">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3">
-        <f>C26+D26</f>
-        <v>7</v>
-      </c>
-      <c r="F26" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G26" s="3">
-        <f t="shared" si="5"/>
-        <v>3.6</v>
-      </c>
-      <c r="H26" s="3">
-        <f>F26+G26</f>
-        <v>8.4</v>
-      </c>
-      <c r="I26" s="3">
-        <f>F26*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J26" s="3">
-        <f>G26*$N$3</f>
-        <v>3.24</v>
-      </c>
-      <c r="K26" s="3">
-        <f>H26*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="97" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="3">
-        <v>5</v>
-      </c>
-      <c r="D27" s="3">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <f t="shared" ref="E27:E38" si="6">C27+D27</f>
-        <v>10</v>
-      </c>
-      <c r="F27" s="3">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="G27" s="3">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="H27" s="3">
-        <f t="shared" ref="H27:H40" si="7">F27+G27</f>
-        <v>12</v>
-      </c>
-      <c r="I27" s="3">
-        <f>F27*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J27" s="3">
-        <f>G27*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="K27" s="3">
-        <f>H27*$N$3</f>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="97"/>
-      <c r="B28" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="3">
-        <v>4</v>
-      </c>
-      <c r="D28" s="3">
-        <v>4</v>
-      </c>
-      <c r="E28" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="F28" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G28" s="3">
-        <f t="shared" si="5"/>
-        <v>4.8</v>
-      </c>
-      <c r="H28" s="3">
-        <f t="shared" si="7"/>
-        <v>9.6</v>
-      </c>
-      <c r="I28" s="3">
-        <f>F28*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J28" s="3">
-        <f>G28*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="K28" s="3">
-        <f>H28*$N$3</f>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="97" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="3">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="F29" s="3">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="G29" s="3">
-        <f t="shared" si="5"/>
-        <v>4.8</v>
-      </c>
-      <c r="H29" s="3">
-        <f t="shared" si="7"/>
-        <v>10.8</v>
-      </c>
-      <c r="I29" s="3">
-        <f>F29*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J29" s="3">
-        <f>G29*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="K29" s="3">
-        <f>H29*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="97"/>
-      <c r="B30" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="3">
-        <v>4</v>
-      </c>
-      <c r="D30" s="3">
-        <v>3</v>
-      </c>
-      <c r="E30" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="F30" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G30" s="3">
-        <f t="shared" si="5"/>
-        <v>3.6</v>
-      </c>
-      <c r="H30" s="3">
-        <f t="shared" si="7"/>
-        <v>8.4</v>
-      </c>
-      <c r="I30" s="3">
-        <f>F30*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J30" s="3">
-        <f>G30*$N$3</f>
-        <v>3.24</v>
-      </c>
-      <c r="K30" s="3">
-        <f>H30*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="97" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="3">
-        <v>5</v>
-      </c>
-      <c r="D31" s="3">
-        <v>4</v>
-      </c>
-      <c r="E31" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="F31" s="3">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="G31" s="3">
-        <f t="shared" si="5"/>
-        <v>4.8</v>
-      </c>
-      <c r="H31" s="3">
-        <f t="shared" si="7"/>
-        <v>10.8</v>
-      </c>
-      <c r="I31" s="3">
-        <f>F31*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J31" s="3">
-        <f>G31*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="K31" s="3">
-        <f>H31*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="97"/>
-      <c r="B32" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" s="3">
-        <v>4</v>
-      </c>
-      <c r="D32" s="3">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="F32" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G32" s="3">
-        <f t="shared" si="5"/>
-        <v>3.6</v>
-      </c>
-      <c r="H32" s="3">
-        <f t="shared" si="7"/>
-        <v>8.4</v>
-      </c>
-      <c r="I32" s="3">
-        <f>F32*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J32" s="3">
-        <f>G32*$N$3</f>
-        <v>3.24</v>
-      </c>
-      <c r="K32" s="3">
-        <f>H32*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="97" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="3">
-        <v>5</v>
-      </c>
-      <c r="D33" s="3">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="F33" s="3">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="G33" s="3">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="H33" s="3">
-        <f t="shared" si="7"/>
-        <v>12</v>
-      </c>
-      <c r="I33" s="3">
-        <f>F33*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J33" s="3">
-        <f>G33*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="K33" s="3">
-        <f>H33*$N$3</f>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="97"/>
-      <c r="B34" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="3">
-        <v>4</v>
-      </c>
-      <c r="D34" s="3">
-        <v>4</v>
-      </c>
-      <c r="E34" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="F34" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G34" s="3">
-        <f t="shared" si="5"/>
-        <v>4.8</v>
-      </c>
-      <c r="H34" s="3">
-        <f t="shared" si="7"/>
-        <v>9.6</v>
-      </c>
-      <c r="I34" s="3">
-        <f>F34*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J34" s="3">
-        <f>G34*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="K34" s="3">
-        <f>H34*$N$3</f>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="97" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="3">
-        <v>5</v>
-      </c>
-      <c r="D35" s="3">
-        <v>7</v>
-      </c>
-      <c r="E35" s="3">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="F35" s="3">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="G35" s="3">
-        <f t="shared" si="5"/>
-        <v>8.4</v>
-      </c>
-      <c r="H35" s="3">
-        <f t="shared" si="7"/>
-        <v>14.4</v>
-      </c>
-      <c r="I35" s="3">
-        <f>F35*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J35" s="3">
-        <f>G35*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="K35" s="3">
-        <f>H35*$N$3</f>
-        <v>12.96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="97"/>
-      <c r="B36" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="3">
-        <v>4</v>
-      </c>
-      <c r="D36" s="3">
-        <v>4</v>
-      </c>
-      <c r="E36" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="F36" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G36" s="3">
-        <f t="shared" si="5"/>
-        <v>4.8</v>
-      </c>
-      <c r="H36" s="3">
-        <f t="shared" si="7"/>
-        <v>9.6</v>
-      </c>
-      <c r="I36" s="3">
-        <f>F36*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J36" s="3">
-        <f>G36*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="K36" s="3">
-        <f>H36*$N$3</f>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="97" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="3">
-        <v>5</v>
-      </c>
-      <c r="D37" s="3">
-        <v>29</v>
-      </c>
-      <c r="E37" s="3">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-      <c r="F37" s="3">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="G37" s="3">
-        <f t="shared" si="5"/>
-        <v>34.799999999999997</v>
-      </c>
-      <c r="H37" s="3">
-        <f t="shared" si="7"/>
-        <v>40.799999999999997</v>
-      </c>
-      <c r="I37" s="3">
-        <f>F37*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J37" s="3">
-        <f>G37*$N$3</f>
-        <v>31.319999999999997</v>
-      </c>
-      <c r="K37" s="3">
-        <f>H37*$N$3</f>
-        <v>36.72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="97"/>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="3">
-        <v>4</v>
-      </c>
-      <c r="D38" s="3">
-        <v>18</v>
-      </c>
-      <c r="E38" s="3">
-        <f t="shared" si="6"/>
-        <v>22</v>
-      </c>
-      <c r="F38" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G38" s="3">
-        <f t="shared" si="5"/>
-        <v>21.6</v>
-      </c>
-      <c r="H38" s="3">
-        <f t="shared" si="7"/>
-        <v>26.400000000000002</v>
-      </c>
-      <c r="I38" s="3">
-        <f>F38*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J38" s="3">
-        <f>G38*$N$3</f>
-        <v>19.440000000000001</v>
-      </c>
-      <c r="K38" s="3">
-        <f>H38*$N$3</f>
-        <v>23.76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="97" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="3">
-        <v>5</v>
-      </c>
-      <c r="D39" s="3">
-        <v>9</v>
-      </c>
-      <c r="E39" s="3">
-        <f>C39+D39</f>
-        <v>14</v>
-      </c>
-      <c r="F39" s="3">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="G39" s="3">
-        <f t="shared" si="5"/>
-        <v>10.8</v>
-      </c>
-      <c r="H39" s="3">
-        <f t="shared" si="7"/>
-        <v>16.8</v>
-      </c>
-      <c r="I39" s="3">
-        <f>F39*$N$3</f>
-        <v>5.4</v>
-      </c>
-      <c r="J39" s="3">
-        <f>G39*$N$3</f>
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="K39" s="3">
-        <f>H39*$N$3</f>
-        <v>15.120000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="97"/>
-      <c r="B40" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="3">
-        <v>4</v>
-      </c>
-      <c r="D40" s="3">
-        <v>7</v>
-      </c>
-      <c r="E40" s="3">
-        <f>C40+D40</f>
-        <v>11</v>
-      </c>
-      <c r="F40" s="3">
-        <f t="shared" si="4"/>
-        <v>4.8</v>
-      </c>
-      <c r="G40" s="3">
-        <f t="shared" si="5"/>
-        <v>8.4</v>
-      </c>
-      <c r="H40" s="3">
-        <f t="shared" si="7"/>
-        <v>13.2</v>
-      </c>
-      <c r="I40" s="3">
-        <f>F40*$N$3</f>
-        <v>4.32</v>
-      </c>
-      <c r="J40" s="3">
-        <f>G40*$N$3</f>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="K40" s="3">
-        <f>H40*$N$3</f>
-        <v>11.879999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G42" s="98" t="s">
-        <v>160</v>
-      </c>
-      <c r="H42" s="98"/>
-      <c r="I42" s="99" t="s">
-        <v>84</v>
-      </c>
-      <c r="J42" s="99"/>
-      <c r="K42" s="99"/>
-    </row>
-    <row r="43" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G43" s="98"/>
-      <c r="H43" s="98"/>
-      <c r="I43" s="99" t="s">
-        <v>159</v>
-      </c>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-    </row>
-    <row r="44" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G44" s="98"/>
-      <c r="H44" s="98"/>
-      <c r="I44" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="J44" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="K44" s="48" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G45" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="H45" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I45" s="48">
-        <f t="shared" ref="I45:K60" si="8">AVERAGE(I25,I5)</f>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J45" s="48">
-        <f t="shared" si="8"/>
-        <v>3.24</v>
-      </c>
-      <c r="K45" s="48">
-        <f t="shared" si="8"/>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G46" s="96"/>
-      <c r="H46" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I46" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J46" s="48">
-        <f t="shared" si="8"/>
-        <v>2.16</v>
-      </c>
-      <c r="K46" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G47" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="H47" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I47" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J47" s="48">
-        <f t="shared" si="8"/>
-        <v>4.32</v>
-      </c>
-      <c r="K47" s="48">
-        <f t="shared" si="8"/>
-        <v>11.88</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G48" s="96"/>
-      <c r="H48" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I48" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J48" s="48">
-        <f t="shared" si="8"/>
-        <v>3.24</v>
-      </c>
-      <c r="K48" s="48">
-        <f t="shared" si="8"/>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="49" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G49" s="96" t="s">
-        <v>83</v>
-      </c>
-      <c r="H49" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I49" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J49" s="48">
-        <f t="shared" si="8"/>
-        <v>3.24</v>
-      </c>
-      <c r="K49" s="48">
-        <f t="shared" si="8"/>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="50" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G50" s="96"/>
-      <c r="H50" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I50" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J50" s="48">
-        <f t="shared" si="8"/>
-        <v>2.16</v>
-      </c>
-      <c r="K50" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="51" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G51" s="96" t="s">
-        <v>78</v>
-      </c>
-      <c r="H51" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I51" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J51" s="48">
-        <f t="shared" si="8"/>
-        <v>3.24</v>
-      </c>
-      <c r="K51" s="48">
-        <f t="shared" si="8"/>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="52" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G52" s="96"/>
-      <c r="H52" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I52" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J52" s="48">
-        <f t="shared" si="8"/>
-        <v>2.16</v>
-      </c>
-      <c r="K52" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-    </row>
-    <row r="53" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G53" s="96" t="s">
-        <v>79</v>
-      </c>
-      <c r="H53" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I53" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J53" s="48">
-        <f t="shared" si="8"/>
-        <v>4.32</v>
-      </c>
-      <c r="K53" s="48">
-        <f t="shared" si="8"/>
-        <v>11.88</v>
-      </c>
-    </row>
-    <row r="54" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G54" s="96"/>
-      <c r="H54" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I54" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J54" s="48">
-        <f t="shared" si="8"/>
-        <v>3.24</v>
-      </c>
-      <c r="K54" s="48">
-        <f t="shared" si="8"/>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="55" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G55" s="96" t="s">
-        <v>80</v>
-      </c>
-      <c r="H55" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I55" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J55" s="48">
-        <f t="shared" si="8"/>
-        <v>6.48</v>
-      </c>
-      <c r="K55" s="48">
-        <f t="shared" si="8"/>
-        <v>14.040000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G56" s="96"/>
-      <c r="H56" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I56" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J56" s="48">
-        <f t="shared" si="8"/>
-        <v>3.24</v>
-      </c>
-      <c r="K56" s="48">
-        <f t="shared" si="8"/>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="57" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G57" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="H57" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I57" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J57" s="48">
-        <f t="shared" si="8"/>
-        <v>30.24</v>
-      </c>
-      <c r="K57" s="48">
-        <f t="shared" si="8"/>
-        <v>37.799999999999997</v>
-      </c>
-    </row>
-    <row r="58" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G58" s="96"/>
-      <c r="H58" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I58" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J58" s="48">
-        <f t="shared" si="8"/>
-        <v>18.36</v>
-      </c>
-      <c r="K58" s="48">
-        <f t="shared" si="8"/>
-        <v>23.759999999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G59" s="96" t="s">
-        <v>82</v>
-      </c>
-      <c r="H59" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I59" s="48">
-        <f t="shared" si="8"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="J59" s="48">
-        <f t="shared" si="8"/>
-        <v>8.64</v>
-      </c>
-      <c r="K59" s="48">
-        <f t="shared" si="8"/>
-        <v>16.200000000000003</v>
-      </c>
-    </row>
-    <row r="60" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G60" s="96"/>
-      <c r="H60" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="I60" s="48">
-        <f t="shared" si="8"/>
-        <v>5.4</v>
-      </c>
-      <c r="J60" s="48">
-        <f t="shared" si="8"/>
-        <v>6.48</v>
-      </c>
-      <c r="K60" s="48">
-        <f t="shared" si="8"/>
-        <v>11.879999999999999</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="11">
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G1:H3"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A22:B24"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="G42:H44"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="G59:G60"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="G53:G54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -9874,7 +8210,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -9894,108 +8230,108 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="118" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="78"/>
+      <c r="P2" s="103" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="77"/>
     </row>
     <row r="3" spans="2:23" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="H3" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="I3" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="P3" s="71" t="s">
+      <c r="H3" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="P3" s="70" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" s="70" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="S3" t="s">
+        <v>133</v>
+      </c>
+      <c r="T3" t="s">
+        <v>134</v>
+      </c>
+      <c r="U3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B4" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="N4" s="64" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" s="65"/>
+      <c r="P4" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q4" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="R4" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="S4" t="s">
         <v>125</v>
       </c>
-      <c r="Q3" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="R3" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="S3" t="s">
-        <v>136</v>
-      </c>
-      <c r="T3" t="s">
-        <v>137</v>
-      </c>
-      <c r="U3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B4" s="107" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="N4" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="O4" s="66"/>
-      <c r="P4" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q4" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="R4" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="T4" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="U4" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="T4" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="U4" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="V4" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="W4" s="74" t="s">
-        <v>130</v>
+      <c r="V4" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="W4" s="73" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B5" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="52"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="N5" s="113" t="s">
+      <c r="B5" s="113" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="113" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="113" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="113" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="113" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="51"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="N5" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="O5" s="67" t="s">
-        <v>120</v>
+      <c r="O5" s="66" t="s">
+        <v>117</v>
       </c>
       <c r="P5">
         <v>179.84387805414332</v>
@@ -10022,31 +8358,31 @@
         <f t="shared" ref="V5:V10" si="3">U5/1.1</f>
         <v>56.633296681393638</v>
       </c>
-      <c r="W5" s="77">
+      <c r="W5" s="76">
         <f t="shared" ref="W5:W10" si="4">V5*0.85</f>
         <v>48.138302179184592</v>
       </c>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B6" s="110" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="57">
+      <c r="B6" s="114" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="56">
         <v>2377.0679331018223</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="56">
         <v>1682.858557540909</v>
       </c>
-      <c r="N6" s="114"/>
-      <c r="O6" s="68" t="s">
-        <v>121</v>
+      <c r="N6" s="99"/>
+      <c r="O6" s="67" t="s">
+        <v>118</v>
       </c>
       <c r="P6">
         <v>133.63285074014715</v>
@@ -10079,27 +8415,27 @@
       </c>
     </row>
     <row r="7" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="109" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="109" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="109" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="109" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7" s="109" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="52"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="N7" s="115"/>
-      <c r="O7" s="69" t="s">
-        <v>122</v>
+      <c r="B7" s="113" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="51"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="68" t="s">
+        <v>119</v>
       </c>
       <c r="P7">
         <v>69.581200395253731</v>
@@ -10132,27 +8468,27 @@
       </c>
     </row>
     <row r="8" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B8" s="101" t="s">
+      <c r="B8" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="H8" s="61">
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="60">
         <v>96.839722360782176</v>
       </c>
-      <c r="I8" s="61">
+      <c r="I8" s="60">
         <v>88.514528269267828</v>
       </c>
-      <c r="N8" s="116" t="s">
+      <c r="N8" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="O8" s="70" t="s">
-        <v>123</v>
+      <c r="O8" s="69" t="s">
+        <v>120</v>
       </c>
       <c r="P8">
         <v>123.39746220558699</v>
@@ -10179,31 +8515,31 @@
         <f t="shared" si="3"/>
         <v>40.96194396425917</v>
       </c>
-      <c r="W8" s="77">
+      <c r="W8" s="76">
         <f t="shared" si="4"/>
         <v>34.817652369620291</v>
       </c>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B9" s="101" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="53" t="s">
+      <c r="B9" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="60">
+        <v>48.63410511864155</v>
+      </c>
+      <c r="I9" s="60">
+        <v>20.899146092495229</v>
+      </c>
+      <c r="N9" s="99"/>
+      <c r="O9" s="67" t="s">
         <v>118</v>
-      </c>
-      <c r="H9" s="61">
-        <v>48.63410511864155</v>
-      </c>
-      <c r="I9" s="61">
-        <v>20.899146092495229</v>
-      </c>
-      <c r="N9" s="114"/>
-      <c r="O9" s="68" t="s">
-        <v>121</v>
       </c>
       <c r="P9">
         <v>111.92891503652041</v>
@@ -10236,25 +8572,25 @@
       </c>
     </row>
     <row r="10" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B10" s="101" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="61">
+      <c r="B10" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="106"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="60">
         <v>1.7292513020497582</v>
       </c>
-      <c r="I10" s="61">
+      <c r="I10" s="60">
         <v>7.7426107989228346E-2</v>
       </c>
-      <c r="N10" s="117"/>
-      <c r="O10" s="68" t="s">
-        <v>122</v>
+      <c r="N10" s="102"/>
+      <c r="O10" s="67" t="s">
+        <v>119</v>
       </c>
       <c r="P10">
         <v>56.302405988853621</v>
@@ -10287,77 +8623,77 @@
       </c>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="106"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="60">
+        <v>34.548563180842756</v>
+      </c>
+      <c r="I11" s="60">
+        <v>5.8381374984485923</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B12" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="60">
+        <v>7.1651883661885112</v>
+      </c>
+      <c r="I12" s="60">
+        <v>27.039400954501179</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B13" s="105" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="60">
+        <v>13.095303863704578</v>
+      </c>
+      <c r="I13" s="60">
+        <v>10.244046489558489</v>
+      </c>
+      <c r="T13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B14" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="61">
-        <v>34.548563180842756</v>
-      </c>
-      <c r="I11" s="61">
-        <v>5.8381374984485923</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B12" s="101" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12" s="61">
-        <v>7.1651883661885112</v>
-      </c>
-      <c r="I12" s="61">
-        <v>27.039400954501179</v>
-      </c>
-    </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B13" s="101" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="H13" s="61">
-        <v>13.095303863704578</v>
-      </c>
-      <c r="I13" s="61">
-        <v>10.244046489558489</v>
-      </c>
-      <c r="T13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B14" s="104" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="H14" s="62">
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="61">
         <v>202.01213419220934</v>
       </c>
-      <c r="I14" s="62">
+      <c r="I14" s="61">
         <v>152.61268541226053</v>
       </c>
       <c r="T14">
@@ -10365,91 +8701,91 @@
       </c>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G16" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="61">
+      <c r="G16" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="60">
         <v>20.678863793754342</v>
       </c>
-      <c r="I16" s="61">
+      <c r="I16" s="60">
         <v>18.901126823034645</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G17" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="61">
+      <c r="G17" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="60">
         <v>14.217207949332485</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="60">
         <v>6.1094473772191291</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G18" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" s="61">
+      <c r="G18" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="60">
         <v>0.72434878540260272</v>
       </c>
-      <c r="I18" s="61">
+      <c r="I18" s="60">
         <v>3.2432248114527967E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G19" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="H19" s="61">
+      <c r="G19" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="60">
         <v>0.54386348159282671</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="60">
         <v>9.1903960500577753E-2</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G20" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="H20" s="61">
+      <c r="G20" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="60">
         <v>1.2037516455196697</v>
       </c>
-      <c r="I20" s="61">
+      <c r="I20" s="60">
         <v>4.5426193603561984</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G21" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="61">
+      <c r="G21" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" s="60">
         <v>4.7928812141158756</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="60">
         <v>3.7493210151784071</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F22" t="s">
-        <v>139</v>
-      </c>
-      <c r="G22" s="64" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="62">
+        <v>136</v>
+      </c>
+      <c r="G22" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="61">
         <v>42.160916869717802</v>
       </c>
-      <c r="I22" s="62">
+      <c r="I22" s="61">
         <v>33.426850784403484</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F23" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="64" t="s">
-        <v>119</v>
+        <v>108</v>
+      </c>
+      <c r="G23" s="63" t="s">
+        <v>116</v>
       </c>
       <c r="H23" s="2">
         <f>AVERAGE(R5:R7)*C34/1000</f>
@@ -10462,10 +8798,10 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F24" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="64" t="s">
-        <v>119</v>
+        <v>124</v>
+      </c>
+      <c r="G24" s="63" t="s">
+        <v>116</v>
       </c>
       <c r="H24" s="2">
         <f>H22+H23</f>
@@ -10478,7 +8814,7 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F25" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H25" s="4">
         <f>H24/1.1</f>
@@ -10491,82 +8827,77 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F26" t="s">
-        <v>134</v>
-      </c>
-      <c r="H26" s="77">
+        <v>131</v>
+      </c>
+      <c r="H26" s="76">
         <f>H25*0.85</f>
         <v>34.010335624718429</v>
       </c>
-      <c r="I26" s="77">
+      <c r="I26" s="76">
         <f>I25*0.85</f>
         <v>26.514943282896866</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="2:9" ht="44.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="58"/>
-      <c r="C28" s="76" t="s">
+      <c r="B28" s="57"/>
+      <c r="C28" s="75" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+    </row>
+    <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="59">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="59">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="59">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="75"/>
-    </row>
-    <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" s="60">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="59" t="s">
+      <c r="C32" s="59">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="60">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" s="60">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="60">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" s="60">
+      <c r="C33" s="59">
         <v>168</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="60">
+      <c r="B34" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="59">
         <v>366</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
@@ -10576,6 +8907,11 @@
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10602,28 +8938,28 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="88" t="s">
+      <c r="B5" s="95"/>
+      <c r="C5" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88" t="s">
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="93" t="s">
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="92" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="98"/>
-      <c r="B6" s="98"/>
+      <c r="A6" s="95"/>
+      <c r="B6" s="95"/>
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
@@ -10631,7 +8967,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>17</v>
@@ -10640,33 +8976,33 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="93"/>
-      <c r="L6" s="37" t="s">
+      <c r="J6" s="92"/>
+      <c r="L6" s="36" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="92" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="38">
         <v>425.5</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <v>591.13442850000001</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="38">
         <v>588.97248049319296</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="38">
         <v>761.971</v>
       </c>
       <c r="G7" s="5">
@@ -10682,25 +9018,25 @@
         <v>15.239420000000001</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="L7" s="37">
+      <c r="L7" s="36">
         <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="93"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="38">
         <v>228.50746724999999</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
         <v>649.59988399999997</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="38">
         <v>642.76818092668395</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="38">
         <v>979.96219599999995</v>
       </c>
       <c r="G8" s="5">
@@ -10716,25 +9052,25 @@
         <v>19.599243919999999</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="L8" s="37">
+      <c r="L8" s="36">
         <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="93"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="38">
         <v>220</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="38">
         <v>361.53147485</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="38">
         <v>397.63088584624899</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="38">
         <v>589.12645299999997</v>
       </c>
       <c r="G9" s="5">
@@ -10750,25 +9086,25 @@
         <v>11.78252906</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="L9" s="37">
+      <c r="L9" s="36">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="93"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="38">
         <v>370.01868180000002</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="38">
         <v>535.40114900000003</v>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="38">
         <v>502.89978438947298</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="38">
         <v>629.42962599999998</v>
       </c>
       <c r="G10" s="5">
@@ -10784,27 +9120,27 @@
         <v>12.588592519999999</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="L10" s="37">
+      <c r="L10" s="36">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="92" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="38">
         <v>106.87967265</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="38">
         <v>426.71363444999997</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="38">
         <v>573.46514913859596</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="38">
         <v>899.65072650000002</v>
       </c>
       <c r="G11" s="5">
@@ -10820,25 +9156,25 @@
         <v>17.99301453</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="38">
         <v>305.5</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="38">
         <v>969.9268945</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="38">
         <v>778.48775533333298</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="38">
         <v>1060.0363715000001</v>
       </c>
       <c r="G12" s="5">
@@ -10854,27 +9190,27 @@
         <v>21.200727430000001</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L12" s="37">
+        <v>219</v>
+      </c>
+      <c r="L12" s="36">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="93"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="38">
         <v>264.69302590000001</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="38">
         <v>476.99999999999898</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="38">
         <v>693.14127412000005</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="38">
         <v>1341.40798</v>
       </c>
       <c r="G13" s="5">
@@ -10890,25 +9226,25 @@
         <v>26.828159599999999</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="93"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="38">
         <v>556.774496</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="38">
         <v>782.75489500000003</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="38">
         <v>782.75489500000003</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="38">
         <v>1008.735294</v>
       </c>
       <c r="G14" s="5">
@@ -10924,27 +9260,27 @@
         <v>20.174705879999998</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L14" s="37">
+        <v>219</v>
+      </c>
+      <c r="L14" s="36">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
+      <c r="A15" s="92"/>
       <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="38">
         <v>301.8292338</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="38">
         <v>331.37734315</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="38">
         <v>347.553312333333</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="38">
         <v>409.45336005000001</v>
       </c>
       <c r="G15" s="5">
@@ -10960,27 +9296,27 @@
         <v>8.1890672010000003</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L15" s="37">
+        <v>219</v>
+      </c>
+      <c r="L15" s="36">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="93"/>
+      <c r="A16" s="92"/>
       <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="38">
         <v>390.70173979999998</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="38">
         <v>590.97850000000005</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="38">
         <v>553.62136794230696</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="38">
         <v>690.17644999999902</v>
       </c>
       <c r="G16" s="5">
@@ -10996,25 +9332,25 @@
         <v>13.80352899999998</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="L16" s="37">
+      <c r="L16" s="36">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="93"/>
-      <c r="B17" s="46" t="s">
+      <c r="A17" s="92"/>
+      <c r="B17" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="46">
         <v>348</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="46">
         <v>457.5</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="46">
         <v>445.5</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="46">
         <v>489</v>
       </c>
       <c r="G17" s="5">
@@ -11030,30 +9366,30 @@
         <v>9.7799999999999994</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="K17" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="L17" s="37">
+        <v>219</v>
+      </c>
+      <c r="K17" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
+      <c r="A18" s="92"/>
       <c r="B18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="38">
         <v>810</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="38">
         <v>810</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="38">
         <v>810</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="38">
         <v>810</v>
       </c>
       <c r="G18" s="5">
@@ -11069,27 +9405,27 @@
         <v>16.2</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L18" s="37">
+        <v>219</v>
+      </c>
+      <c r="L18" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="93"/>
+      <c r="A19" s="92"/>
       <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="38">
         <v>314.5</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="38">
         <v>365</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="38">
         <v>380.76225355999998</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="38">
         <v>490</v>
       </c>
       <c r="G19" s="5">
@@ -11105,9 +9441,9 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L19" s="37">
+        <v>219</v>
+      </c>
+      <c r="L19" s="36">
         <v>5</v>
       </c>
     </row>
@@ -11148,7 +9484,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
@@ -11157,366 +9493,366 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="37" t="s">
+      <c r="A56" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="37" t="s">
+      <c r="C56" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="37" t="s">
+      <c r="D56" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="D56" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="37" t="s">
+      <c r="J56" s="37">
+        <v>0.25</v>
+      </c>
+      <c r="K56" s="37">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="J56" s="38">
-        <v>0.25</v>
-      </c>
-      <c r="K56" s="38">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="37" t="s">
+      <c r="B57" s="36">
+        <v>1</v>
+      </c>
+      <c r="C57" s="36">
+        <v>368.92602740000001</v>
+      </c>
+      <c r="D57" s="36">
+        <v>368.92602740000001</v>
+      </c>
+      <c r="E57" s="36">
+        <v>368.92602740000001</v>
+      </c>
+      <c r="F57" s="36">
+        <v>368.92602740000001</v>
+      </c>
+      <c r="J57" s="36">
+        <v>368.92602740000001</v>
+      </c>
+      <c r="K57" s="36">
+        <v>368.92602740000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="37">
+      <c r="B58" s="36">
+        <v>3</v>
+      </c>
+      <c r="C58" s="36">
+        <v>305.5</v>
+      </c>
+      <c r="D58" s="36">
+        <v>969.9268945</v>
+      </c>
+      <c r="E58" s="36">
+        <v>778.48775533333298</v>
+      </c>
+      <c r="F58" s="36">
+        <v>1060.0363715000001</v>
+      </c>
+      <c r="J58" s="36">
+        <v>637.71344724999994</v>
+      </c>
+      <c r="K58" s="36">
+        <v>1014.981633</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="36">
+        <v>3</v>
+      </c>
+      <c r="C59" s="36">
+        <v>301.8292338</v>
+      </c>
+      <c r="D59" s="36">
+        <v>331.37734315</v>
+      </c>
+      <c r="E59" s="36">
+        <v>347.553312333333</v>
+      </c>
+      <c r="F59" s="36">
+        <v>409.45336005000001</v>
+      </c>
+      <c r="J59" s="36">
+        <v>316.603288475</v>
+      </c>
+      <c r="K59" s="36">
+        <v>370.41535160000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" s="36">
         <v>1</v>
       </c>
-      <c r="C57" s="37">
-        <v>368.92602740000001</v>
-      </c>
-      <c r="D57" s="37">
-        <v>368.92602740000001</v>
-      </c>
-      <c r="E57" s="37">
-        <v>368.92602740000001</v>
-      </c>
-      <c r="F57" s="37">
-        <v>368.92602740000001</v>
-      </c>
-      <c r="J57" s="37">
-        <v>368.92602740000001</v>
-      </c>
-      <c r="K57" s="37">
-        <v>368.92602740000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="B58" s="37">
+      <c r="C60" s="36">
+        <v>810</v>
+      </c>
+      <c r="D60" s="36">
+        <v>810</v>
+      </c>
+      <c r="E60" s="36">
+        <v>810</v>
+      </c>
+      <c r="F60" s="36">
+        <v>810</v>
+      </c>
+      <c r="J60" s="36">
+        <v>810</v>
+      </c>
+      <c r="K60" s="36">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="37">
-        <v>305.5</v>
-      </c>
-      <c r="D58" s="37">
-        <v>969.9268945</v>
-      </c>
-      <c r="E58" s="37">
-        <v>778.48775533333298</v>
-      </c>
-      <c r="F58" s="37">
-        <v>1060.0363715000001</v>
-      </c>
-      <c r="J58" s="37">
-        <v>637.71344724999994</v>
-      </c>
-      <c r="K58" s="37">
-        <v>1014.981633</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="37" t="s">
+      <c r="B61" s="36">
+        <v>193</v>
+      </c>
+      <c r="C61" s="36">
+        <v>228.50746724999999</v>
+      </c>
+      <c r="D61" s="36">
+        <v>649.59988399999997</v>
+      </c>
+      <c r="E61" s="36">
+        <v>642.76818092668395</v>
+      </c>
+      <c r="F61" s="36">
+        <v>979.96219599999995</v>
+      </c>
+      <c r="J61" s="36">
+        <v>501.887035499999</v>
+      </c>
+      <c r="K61" s="36">
+        <v>763.68372950000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="36">
+        <v>57</v>
+      </c>
+      <c r="C62" s="36">
+        <v>106.87967265</v>
+      </c>
+      <c r="D62" s="36">
+        <v>426.71363444999997</v>
+      </c>
+      <c r="E62" s="36">
+        <v>573.46514913859596</v>
+      </c>
+      <c r="F62" s="36">
+        <v>899.65072650000002</v>
+      </c>
+      <c r="J62" s="36">
+        <v>330.59104200000002</v>
+      </c>
+      <c r="K62" s="36">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="36">
+        <v>5</v>
+      </c>
+      <c r="C63" s="36">
+        <v>314.5</v>
+      </c>
+      <c r="D63" s="36">
+        <v>365</v>
+      </c>
+      <c r="E63" s="36">
+        <v>380.76225355999998</v>
+      </c>
+      <c r="F63" s="36">
+        <v>490</v>
+      </c>
+      <c r="J63" s="36">
+        <v>329.8112678</v>
+      </c>
+      <c r="K63" s="36">
+        <v>404.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="B59" s="37">
-        <v>3</v>
-      </c>
-      <c r="C59" s="37">
-        <v>301.8292338</v>
-      </c>
-      <c r="D59" s="37">
-        <v>331.37734315</v>
-      </c>
-      <c r="E59" s="37">
-        <v>347.553312333333</v>
-      </c>
-      <c r="F59" s="37">
-        <v>409.45336005000001</v>
-      </c>
-      <c r="J59" s="37">
-        <v>316.603288475</v>
-      </c>
-      <c r="K59" s="37">
-        <v>370.41535160000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="37" t="s">
+      <c r="B64" s="36">
         <v>13</v>
       </c>
-      <c r="B60" s="37">
-        <v>1</v>
-      </c>
-      <c r="C60" s="37">
-        <v>810</v>
-      </c>
-      <c r="D60" s="37">
-        <v>810</v>
-      </c>
-      <c r="E60" s="37">
-        <v>810</v>
-      </c>
-      <c r="F60" s="37">
-        <v>810</v>
-      </c>
-      <c r="J60" s="37">
-        <v>810</v>
-      </c>
-      <c r="K60" s="37">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="37">
-        <v>193</v>
-      </c>
-      <c r="C61" s="37">
-        <v>228.50746724999999</v>
-      </c>
-      <c r="D61" s="37">
-        <v>649.59988399999997</v>
-      </c>
-      <c r="E61" s="37">
-        <v>642.76818092668395</v>
-      </c>
-      <c r="F61" s="37">
-        <v>979.96219599999995</v>
-      </c>
-      <c r="J61" s="37">
-        <v>501.887035499999</v>
-      </c>
-      <c r="K61" s="37">
-        <v>763.68372950000003</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" s="37">
-        <v>57</v>
-      </c>
-      <c r="C62" s="37">
-        <v>106.87967265</v>
-      </c>
-      <c r="D62" s="37">
-        <v>426.71363444999997</v>
-      </c>
-      <c r="E62" s="37">
-        <v>573.46514913859596</v>
-      </c>
-      <c r="F62" s="37">
-        <v>899.65072650000002</v>
-      </c>
-      <c r="J62" s="37">
-        <v>330.59104200000002</v>
-      </c>
-      <c r="K62" s="37">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B63" s="37">
-        <v>5</v>
-      </c>
-      <c r="C63" s="37">
-        <v>314.5</v>
-      </c>
-      <c r="D63" s="37">
-        <v>365</v>
-      </c>
-      <c r="E63" s="37">
-        <v>380.76225355999998</v>
-      </c>
-      <c r="F63" s="37">
-        <v>490</v>
-      </c>
-      <c r="J63" s="37">
-        <v>329.8112678</v>
-      </c>
-      <c r="K63" s="37">
-        <v>404.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="37" t="s">
+      <c r="C64" s="36">
+        <v>390.70173979999998</v>
+      </c>
+      <c r="D64" s="36">
+        <v>590.97850000000005</v>
+      </c>
+      <c r="E64" s="36">
+        <v>553.62136794230696</v>
+      </c>
+      <c r="F64" s="36">
+        <v>690.17644999999902</v>
+      </c>
+      <c r="J64" s="36">
+        <v>511</v>
+      </c>
+      <c r="K64" s="36">
+        <v>618.79840000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="36">
+        <v>40</v>
+      </c>
+      <c r="C65" s="36">
+        <v>220</v>
+      </c>
+      <c r="D65" s="36">
+        <v>361.53147485</v>
+      </c>
+      <c r="E65" s="36">
+        <v>397.63088584624899</v>
+      </c>
+      <c r="F65" s="36">
+        <v>589.12645299999997</v>
+      </c>
+      <c r="J65" s="36">
+        <v>303.13484627499997</v>
+      </c>
+      <c r="K65" s="36">
+        <v>525.86608787499995</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="B64" s="37">
-        <v>13</v>
-      </c>
-      <c r="C64" s="37">
-        <v>390.70173979999998</v>
-      </c>
-      <c r="D64" s="37">
-        <v>590.97850000000005</v>
-      </c>
-      <c r="E64" s="37">
-        <v>553.62136794230696</v>
-      </c>
-      <c r="F64" s="37">
-        <v>690.17644999999902</v>
-      </c>
-      <c r="J64" s="37">
-        <v>511</v>
-      </c>
-      <c r="K64" s="37">
-        <v>618.79840000000002</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="37">
-        <v>40</v>
-      </c>
-      <c r="C65" s="37">
-        <v>220</v>
-      </c>
-      <c r="D65" s="37">
-        <v>361.53147485</v>
-      </c>
-      <c r="E65" s="37">
-        <v>397.63088584624899</v>
-      </c>
-      <c r="F65" s="37">
-        <v>589.12645299999997</v>
-      </c>
-      <c r="J65" s="37">
-        <v>303.13484627499997</v>
-      </c>
-      <c r="K65" s="37">
-        <v>525.86608787499995</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="37" t="s">
+      <c r="B66" s="36">
+        <v>25</v>
+      </c>
+      <c r="C66" s="36">
+        <v>264.69302590000001</v>
+      </c>
+      <c r="D66" s="36">
+        <v>476.99999999999898</v>
+      </c>
+      <c r="E66" s="36">
+        <v>693.14127412000005</v>
+      </c>
+      <c r="F66" s="36">
+        <v>1341.40798</v>
+      </c>
+      <c r="J66" s="36">
+        <v>419.5</v>
+      </c>
+      <c r="K66" s="36">
+        <v>930.115377499999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B66" s="37">
-        <v>25</v>
-      </c>
-      <c r="C66" s="37">
-        <v>264.69302590000001</v>
-      </c>
-      <c r="D66" s="37">
-        <v>476.99999999999898</v>
-      </c>
-      <c r="E66" s="37">
-        <v>693.14127412000005</v>
-      </c>
-      <c r="F66" s="37">
-        <v>1341.40798</v>
-      </c>
-      <c r="J66" s="37">
-        <v>419.5</v>
-      </c>
-      <c r="K66" s="37">
-        <v>930.115377499999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="37" t="s">
+      <c r="B67" s="36">
+        <v>19</v>
+      </c>
+      <c r="C67" s="36">
+        <v>370.01868180000002</v>
+      </c>
+      <c r="D67" s="36">
+        <v>535.40114900000003</v>
+      </c>
+      <c r="E67" s="36">
+        <v>502.89978438947298</v>
+      </c>
+      <c r="F67" s="36">
+        <v>629.42962599999998</v>
+      </c>
+      <c r="J67" s="36">
+        <v>411.70235012500001</v>
+      </c>
+      <c r="K67" s="36">
+        <v>567.27258974999995</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" s="36">
+        <v>382</v>
+      </c>
+      <c r="C68" s="36">
+        <v>425.5</v>
+      </c>
+      <c r="D68" s="36">
+        <v>591.13442850000001</v>
+      </c>
+      <c r="E68" s="36">
+        <v>588.97248049319296</v>
+      </c>
+      <c r="F68" s="36">
+        <v>761.971</v>
+      </c>
+      <c r="J68" s="36">
+        <v>548.98450949999994</v>
+      </c>
+      <c r="K68" s="36">
+        <v>634.66583787499997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="B67" s="37">
-        <v>19</v>
-      </c>
-      <c r="C67" s="37">
-        <v>370.01868180000002</v>
-      </c>
-      <c r="D67" s="37">
-        <v>535.40114900000003</v>
-      </c>
-      <c r="E67" s="37">
-        <v>502.89978438947298</v>
-      </c>
-      <c r="F67" s="37">
-        <v>629.42962599999998</v>
-      </c>
-      <c r="J67" s="37">
-        <v>411.70235012500001</v>
-      </c>
-      <c r="K67" s="37">
-        <v>567.27258974999995</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="37" t="s">
+      <c r="B69" s="36">
         <v>2</v>
       </c>
-      <c r="B68" s="37">
-        <v>382</v>
-      </c>
-      <c r="C68" s="37">
-        <v>425.5</v>
-      </c>
-      <c r="D68" s="37">
-        <v>591.13442850000001</v>
-      </c>
-      <c r="E68" s="37">
-        <v>588.97248049319296</v>
-      </c>
-      <c r="F68" s="37">
-        <v>761.971</v>
-      </c>
-      <c r="J68" s="37">
-        <v>548.98450949999994</v>
-      </c>
-      <c r="K68" s="37">
-        <v>634.66583787499997</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="B69" s="37">
-        <v>2</v>
-      </c>
-      <c r="C69" s="37">
+      <c r="C69" s="36">
         <v>556.774496</v>
       </c>
-      <c r="D69" s="37">
+      <c r="D69" s="36">
         <v>782.75489500000003</v>
       </c>
-      <c r="E69" s="37">
+      <c r="E69" s="36">
         <v>782.75489500000003</v>
       </c>
-      <c r="F69" s="37">
+      <c r="F69" s="36">
         <v>1008.735294</v>
       </c>
-      <c r="J69" s="37">
+      <c r="J69" s="36">
         <v>669.76469550000002</v>
       </c>
-      <c r="K69" s="37">
+      <c r="K69" s="36">
         <v>895.74509450000005</v>
       </c>
     </row>
